--- a/output/graficos_nacionales/plot_nacional_regiones_m_saldomigr_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_m_saldomigr_a_2019.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:37</t>
+    <t xml:space="preserve">2026-09-09 21:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_m_saldomigr_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_m_saldomigr_a_2019.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:38</t>
+    <t xml:space="preserve">2026-09-16 21:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-4641</v>
+        <v>-1547</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-1257</v>
+        <v>-419</v>
       </c>
     </row>
     <row r="4">
@@ -506,7 +506,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-1962</v>
+        <v>-654</v>
       </c>
     </row>
     <row r="5">
@@ -514,7 +514,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-711</v>
+        <v>-237</v>
       </c>
     </row>
     <row r="6">
@@ -522,7 +522,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>22287</v>
+        <v>7429</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4833</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="8">
@@ -538,7 +538,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>8115</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3717</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="10">
@@ -554,7 +554,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1206</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11">
@@ -562,7 +562,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1893</v>
+        <v>631</v>
       </c>
     </row>
     <row r="12">
@@ -570,7 +570,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>12315</v>
+        <v>4105</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-12339</v>
+        <v>-4113</v>
       </c>
     </row>
     <row r="14">
@@ -586,7 +586,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>5319</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="15">
@@ -594,7 +594,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-9780</v>
+        <v>-3260</v>
       </c>
     </row>
     <row r="16">
@@ -602,7 +602,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>13356</v>
+        <v>4452</v>
       </c>
     </row>
     <row r="17">
@@ -610,7 +610,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-42351</v>
+        <v>-14117</v>
       </c>
     </row>
   </sheetData>
